--- a/integradores/int-basico.xlsx
+++ b/integradores/int-basico.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Reporte semanal de la sucursal Sur: cálculos, formato, gráfica e impresión.</t>
+          <t>Reporte semanal de la sucursal Sur: cálculos, formato, gráfico, logo y resumen.</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. J4:J11 unidades de la semana (suma de Lun a Dom); K4:K11 ventas (precio × unidades); J12 y K12 totales; N4 promedio de ventas por producto; N5 venta mayor.</t>
+          <t>1. Semana: J4:J11 unidades de la semana (suma de Lun a Dom); K4:K11 ventas (precio × unidades); J12 y K12 totales; N4 promedio de ventas por producto; N5 venta mayor.</t>
         </is>
       </c>
     </row>
@@ -495,15 +495,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4. Impresión horizontal ajustada a una página; exporta a PDF y sube ambos archivos.</t>
+          <t>4. Inserta el logo de La Taza (logo-la-taza.png) en la hoja Semana.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5. Agrega una hoja llamada «Resumen» con el total de la semana en B2 (fórmula que tome Semana!K12).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6. Escribe el título del documento «Reporte semanal Sur» (Archivo › Información › Propiedades).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Importante: no cambies los nombres de las hojas ni muevas los datos de lugar. Al terminar, guarda el libro y súbelo en la página del módulo (etapa 4).</t>
         </is>

--- a/integradores/int-basico.xlsx
+++ b/integradores/int-basico.xlsx
@@ -28,7 +28,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="005B3A29"/>
+      <color rgb="000F5E57"/>
       <sz val="16"/>
     </font>
     <font>
@@ -36,7 +36,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="007A4D0E"/>
+      <color rgb="000F5E57"/>
     </font>
   </fonts>
   <fills count="2">
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reto integrador básico · Reporte semanal de ventas</t>
+          <t>Reto integrador · Fundamentos · Reporte semanal de atenciones</t>
         </is>
       </c>
     </row>
@@ -457,7 +457,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Reporte semanal de la sucursal Sur: cálculos, formato, gráfico, logo y resumen.</t>
+          <t>Reporte semanal de la sede Sur: cálculos, clasificación, formato, gráfico, logo y resumen.</t>
         </is>
       </c>
     </row>
@@ -474,52 +474,59 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. Semana: J4:J11 unidades de la semana (suma de Lun a Dom); K4:K11 ventas (precio × unidades); J12 y K12 totales; N4 promedio de ventas por producto; N5 venta mayor.</t>
+          <t>1. J4:J11 atenciones de la semana (suma de Lun a Dom); K4:K11 ingresos (cuota × atenciones); J12 y K12 totales; N4 promedio de ingresos por servicio; N5 ingreso mayor.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2. Formato: título destacado, encabezados A3:K3 en negrita con relleno, precio y ventas en moneda, bordes en A3:K12.</t>
+          <t>2. L4:L11: «Alta demanda» si las atenciones de la semana son mayores o iguales al umbral de N1; si no, «Normal».</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3. Gráfico de columnas o barras de las ventas por producto, con título.</t>
+          <t>3. Formato: título destacado, encabezados A3:L3 en negrita con relleno, cuota e ingresos en moneda, bordes en A3:K12.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4. Inserta el logo de La Taza (logo-la-taza.png) en la hoja Semana.</t>
+          <t>4. Gráfico de columnas o barras de las atenciones por servicio, con título.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5. Agrega una hoja llamada «Resumen» con el total de la semana en B2 (fórmula que tome Semana!K12).</t>
+          <t>5. Inserta el logo de la clínica (logo-vida-sana.png) en la hoja Semana.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6. Escribe el título del documento «Reporte semanal Sur» (Archivo › Información › Propiedades).</t>
+          <t>6. Agrega una hoja llamada «Resumen» con los ingresos de la semana en B2 (fórmula que tome Semana!K12).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7. Escribe el título del documento «Reporte semanal Sur» (Archivo › Información › Propiedades).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Importante: no cambies los nombres de las hojas ni muevas los datos de lugar. Al terminar, guarda el libro y súbelo en la página del módulo (etapa 4).</t>
+      <c r="A13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Importante: no cambies los nombres de las hojas ni muevas los datos de lugar. Al terminar, guarda el libro y súbelo en la página del módulo (etapa 4). Datos ficticios con fines didácticos.</t>
         </is>
       </c>
     </row>
@@ -534,29 +541,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Reporte semanal · Sucursal Sur · Semana 42</t>
-        </is>
+          <t>Reporte semanal de atenciones · Sede Sur · Semana 42</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Umbral de alta demanda</t>
+        </is>
+      </c>
+      <c r="N1" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Precio</t>
+          <t>Cuota</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -596,271 +612,276 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Unidades</t>
+          <t>Atenciones</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Demanda</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Americano</t>
+          <t>Consulta de medicina general</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Promedio por producto</t>
+          <t>Promedio de ingresos por servicio</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Capuchino</t>
+          <t>Consulta de pediatría</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>180</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Venta mayor</t>
+          <t>Ingreso mayor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Latte</t>
+          <t>Consulta de nutrición</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Moka</t>
+          <t>Biometría hemática</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Frappé moka</t>
+          <t>Química sanguínea</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>220</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Croissant</t>
+          <t>Aplicación de inyección</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Concha</t>
+          <t>Toma de glucosa capilar</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brownie</t>
+          <t>Sesión de fisioterapia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
